--- a/results/Int Task Remove ACC 0.3/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC 0.3/Rando_9_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6603655440852936</v>
+        <v>0.6669500240832108</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6668549930353957</v>
+        <v>0.6610616790554174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6684682427066926</v>
+        <v>0.6610616790554174</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6820427118997097</v>
+        <v>0.661430737987685</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6813101266646706</v>
+        <v>0.670677063670802</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6808040537901766</v>
+        <v>0.6889432026764909</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6554053790176654</v>
+        <v>0.6896757879115301</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6799709048778265</v>
+        <v>0.6991066430607809</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6796968769933739</v>
+        <v>0.7011309345587565</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.672933400158819</v>
+        <v>0.7147949021700926</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6291205071794004</v>
+        <v>0.7139783511462306</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6247812984105081</v>
+        <v>0.7108048999570408</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6384927815457515</v>
+        <v>0.7102988270825468</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6117106239504276</v>
+        <v>0.7060181990965542</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6093647890440919</v>
+        <v>0.7064878217061328</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5983681997474517</v>
+        <v>0.677647200489475</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5792324615644975</v>
+        <v>0.67405717484411</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5797385344389914</v>
+        <v>0.67405717484411</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5739396878295169</v>
+        <v>0.7016314748037544</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5957594022156554</v>
+        <v>0.7228025697436765</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5962654750901493</v>
+        <v>0.7272036137834073</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5621629977739303</v>
+        <v>0.6952536547899554</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5591740760508741</v>
+        <v>0.6556484892666987</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5591740760508741</v>
+        <v>0.6434916750198524</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5591740760508741</v>
+        <v>0.6239845997630733</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5471708736347423</v>
+        <v>0.6518352057487276</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5268605907546506</v>
+        <v>0.6442187276253954</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5371776429696551</v>
+        <v>0.6227989898069437</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.539523477875991</v>
+        <v>0.5999085488889178</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5447234987047138</v>
+        <v>0.5999085488889178</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.545872658395928</v>
+        <v>0.618311701836833</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5798436543994168</v>
+        <v>0.618311701836833</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.585634690237838</v>
+        <v>0.6217171980160642</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5744591041045602</v>
+        <v>0.6217171980160642</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6072168270044391</v>
+        <v>0.6509125584180585</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.610074267414765</v>
+        <v>0.664414127081245</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.605656625486546</v>
+        <v>0.6581258054857648</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.621476365908588</v>
+        <v>0.5988235026100993</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6221217308668654</v>
+        <v>0.5988235026100993</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.606164976502597</v>
+        <v>0.6043483213351211</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6423789655935536</v>
+        <v>0.5547840972701356</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6344298788028692</v>
+        <v>0.5517278076467449</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6308001484046499</v>
+        <v>0.5575377195152115</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6479812411315204</v>
+        <v>0.5608957001705351</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5968558392022599</v>
+        <v>0.5743022377859068</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6222125310803598</v>
+        <v>0.5364671882526003</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6222203418514131</v>
+        <v>0.5366517177187341</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.611482484345913</v>
+        <v>0.5333412525873179</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6030748402046422</v>
+        <v>0.5466527591548745</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5306488147154926</v>
+        <v>0.5394196597107411</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5103053360584245</v>
+        <v>0.5375964955673874</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4979630159990627</v>
+        <v>0.5390196831430543</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5300610541937332</v>
+        <v>0.545145605790385</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5293704518531055</v>
+        <v>0.5628627126807868</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5888823437520341</v>
+        <v>0.6045120220784461</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5987883541403596</v>
+        <v>0.599036997018889</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6185782443990262</v>
+        <v>0.5834525560748272</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6197218714607444</v>
+        <v>0.5765774503039691</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6172126612598774</v>
+        <v>0.5769940247601443</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6228357655206529</v>
+        <v>0.5815795982660088</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6277881198172279</v>
+        <v>0.5804945519871904</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6473205800799302</v>
+        <v>0.5805420675110978</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6407891482354167</v>
+        <v>0.5680604553679524</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5906726375672051</v>
+        <v>0.5641313120793574</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5825367431688298</v>
+        <v>0.5734108335394509</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5316697475819154</v>
+        <v>0.5490054284858821</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5379766197586472</v>
+        <v>0.5423679003345614</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5385302081570486</v>
+        <v>0.5370917244880691</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5380241352825547</v>
+        <v>0.5021990575002929</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5433621463998854</v>
+        <v>0.5015559706835726</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5433621463998854</v>
+        <v>0.5040443521616309</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5383821289558302</v>
+        <v>0.5041924313628494</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5313657784084251</v>
+        <v>0.5023526693310075</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5313657784084251</v>
+        <v>0.4935958186338961</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5461180467865187</v>
+        <v>0.4883307080463959</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5195923428407774</v>
+        <v>0.4825871877318823</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5215160706614421</v>
+        <v>0.4829087311402424</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5126443365400888</v>
+        <v>0.4829087311402424</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5117747373628233</v>
+        <v>0.4965141179686788</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4987284715622844</v>
+        <v>0.5080675501516592</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5137381699363422</v>
+        <v>0.4924886418370934</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5068100160120806</v>
+        <v>0.4831694156241457</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5226541650936641</v>
+        <v>0.5031614095838161</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5192265383964487</v>
+        <v>0.5040951221734773</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5192265383964487</v>
+        <v>0.4946333493888072</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5192265383964487</v>
+        <v>0.5048498379265006</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5192265383964487</v>
+        <v>0.5052608797531797</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5069691604722912</v>
+        <v>0.4974400197872866</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5069691604722912</v>
+        <v>0.4906511579468086</v>
       </c>
     </row>
   </sheetData>
